--- a/data/mar.xlsx
+++ b/data/mar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE99143E-19ED-4768-8145-86A2D77CFCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D363B73A-E833-4720-BD91-6A496F7E3EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="38" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="35" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аграрен Университет Пловдив" sheetId="1" r:id="rId1"/>
@@ -6216,10 +6216,10 @@
         <v>18</v>
       </c>
       <c r="H30">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I30">
-        <v>78.430000000000007</v>
+        <v>78.95</v>
       </c>
       <c r="J30">
         <v>1.54</v>
@@ -6456,10 +6456,10 @@
         <v>18</v>
       </c>
       <c r="H36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I36">
-        <v>85.06</v>
+        <v>85.61</v>
       </c>
       <c r="J36">
         <v>1.59</v>
@@ -6497,10 +6497,10 @@
         <v>18</v>
       </c>
       <c r="H37">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I37">
-        <v>31.15</v>
+        <v>31.34</v>
       </c>
       <c r="J37">
         <v>1.71</v>
@@ -6538,10 +6538,10 @@
         <v>18</v>
       </c>
       <c r="H38">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I38">
-        <v>46.11</v>
+        <v>46.4</v>
       </c>
       <c r="J38">
         <v>1.71</v>
@@ -6579,10 +6579,10 @@
         <v>18</v>
       </c>
       <c r="H39">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I39">
-        <v>81.599999999999994</v>
+        <v>82.11</v>
       </c>
       <c r="J39">
         <v>1.71</v>
@@ -6702,10 +6702,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I42">
-        <v>56.13</v>
+        <v>56.47</v>
       </c>
       <c r="J42">
         <v>1.73</v>
@@ -6743,10 +6743,10 @@
         <v>18</v>
       </c>
       <c r="H43">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I43">
-        <v>56.13</v>
+        <v>56.47</v>
       </c>
       <c r="J43">
         <v>1.73</v>
@@ -6866,10 +6866,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I46">
-        <v>85.89</v>
+        <v>86.41</v>
       </c>
       <c r="J46">
         <v>1.73</v>
@@ -6907,10 +6907,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I47">
-        <v>85.89</v>
+        <v>86.41</v>
       </c>
       <c r="J47">
         <v>1.73</v>
@@ -6948,10 +6948,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I48">
-        <v>85.48</v>
+        <v>86</v>
       </c>
       <c r="J48">
         <v>1.73</v>
@@ -6989,10 +6989,10 @@
         <v>18</v>
       </c>
       <c r="H49">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I49">
-        <v>85.48</v>
+        <v>86</v>
       </c>
       <c r="J49">
         <v>1.73</v>
@@ -7725,10 +7725,10 @@
         <v>18</v>
       </c>
       <c r="H2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I2">
-        <v>56.71</v>
+        <v>57.09</v>
       </c>
       <c r="J2">
         <v>1.51</v>
@@ -7766,10 +7766,10 @@
         <v>18</v>
       </c>
       <c r="H3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I3">
-        <v>64.459999999999994</v>
+        <v>64.89</v>
       </c>
       <c r="J3">
         <v>1.55</v>
@@ -8186,10 +8186,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I8">
-        <v>35.72</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="J8">
         <v>1.45</v>
@@ -9109,10 +9109,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I10">
-        <v>620.92999999999995</v>
+        <v>625.29999999999995</v>
       </c>
       <c r="J10">
         <v>1.47</v>
@@ -9150,10 +9150,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I11">
-        <v>518.41</v>
+        <v>522.01</v>
       </c>
       <c r="J11">
         <v>1.49</v>
@@ -9191,10 +9191,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I12">
-        <v>82.05</v>
+        <v>82.62</v>
       </c>
       <c r="J12">
         <v>1.49</v>
@@ -9396,10 +9396,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I17">
-        <v>618.35</v>
+        <v>622.5</v>
       </c>
       <c r="J17">
         <v>1.54</v>
@@ -9437,10 +9437,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I18">
-        <v>89.97</v>
+        <v>90.56</v>
       </c>
       <c r="J18">
         <v>1.56</v>
@@ -11467,10 +11467,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I10">
-        <v>95.84</v>
+        <v>96.46</v>
       </c>
       <c r="J10">
         <v>1.59</v>
@@ -11508,10 +11508,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I11">
-        <v>229.46</v>
+        <v>230.95</v>
       </c>
       <c r="J11">
         <v>1.59</v>
@@ -11549,10 +11549,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I12">
-        <v>167.07</v>
+        <v>168.16</v>
       </c>
       <c r="J12">
         <v>1.57</v>
@@ -11713,10 +11713,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I16">
-        <v>256</v>
+        <v>257.60000000000002</v>
       </c>
       <c r="J16">
         <v>1.63</v>
@@ -13975,10 +13975,10 @@
         <v>18</v>
       </c>
       <c r="H15">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I15">
-        <v>822.37</v>
+        <v>827.82</v>
       </c>
       <c r="J15">
         <v>1.55</v>
@@ -14016,10 +14016,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I16">
-        <v>498.79</v>
+        <v>502.09</v>
       </c>
       <c r="J16">
         <v>1.55</v>
@@ -14057,10 +14057,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I17">
-        <v>418.9</v>
+        <v>421.68</v>
       </c>
       <c r="J17">
         <v>1.55</v>
@@ -14576,10 +14576,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I8">
-        <v>28.99</v>
+        <v>29.19</v>
       </c>
       <c r="J8">
         <v>1.47</v>
@@ -14740,10 +14740,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I12">
-        <v>33.869999999999997</v>
+        <v>34.090000000000003</v>
       </c>
       <c r="J12">
         <v>1.53</v>
@@ -14781,10 +14781,10 @@
         <v>18</v>
       </c>
       <c r="H13">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I13">
-        <v>69.239999999999995</v>
+        <v>69.69</v>
       </c>
       <c r="J13">
         <v>1.6</v>
@@ -14822,10 +14822,10 @@
         <v>18</v>
       </c>
       <c r="H14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I14">
-        <v>46.52</v>
+        <v>46.82</v>
       </c>
       <c r="J14">
         <v>1.59</v>
@@ -14986,10 +14986,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I18">
-        <v>45.23</v>
+        <v>45.51</v>
       </c>
       <c r="J18">
         <v>1.63</v>
@@ -16423,10 +16423,10 @@
         <v>18</v>
       </c>
       <c r="H5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I5">
-        <v>108.9</v>
+        <v>109.64</v>
       </c>
       <c r="J5">
         <v>1.53</v>
@@ -16505,10 +16505,10 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I7">
-        <v>108.77</v>
+        <v>109.45</v>
       </c>
       <c r="J7">
         <v>1.63</v>
@@ -16638,10 +16638,10 @@
         <v>18</v>
       </c>
       <c r="H3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I3">
-        <v>56.86</v>
+        <v>57.24</v>
       </c>
       <c r="J3">
         <v>1.55</v>
@@ -18649,10 +18649,10 @@
         <v>18</v>
       </c>
       <c r="H35">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I35">
-        <v>68.180000000000007</v>
+        <v>68.67</v>
       </c>
       <c r="J35">
         <v>1.46</v>
@@ -18690,10 +18690,10 @@
         <v>18</v>
       </c>
       <c r="H36">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I36">
-        <v>73.400000000000006</v>
+        <v>73.92</v>
       </c>
       <c r="J36">
         <v>1.47</v>
@@ -18731,10 +18731,10 @@
         <v>18</v>
       </c>
       <c r="H37">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I37">
-        <v>59.3</v>
+        <v>59.71</v>
       </c>
       <c r="J37">
         <v>1.49</v>
@@ -18807,10 +18807,10 @@
         <v>18</v>
       </c>
       <c r="H39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I39">
-        <v>56.81</v>
+        <v>57.21</v>
       </c>
       <c r="J39">
         <v>1.48</v>
@@ -18848,10 +18848,10 @@
         <v>18</v>
       </c>
       <c r="H40">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I40">
-        <v>68.099999999999994</v>
+        <v>68.58</v>
       </c>
       <c r="J40">
         <v>1.48</v>
@@ -19568,10 +19568,10 @@
         <v>18</v>
       </c>
       <c r="H58">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I58">
-        <v>51.8</v>
+        <v>52.15</v>
       </c>
       <c r="J58">
         <v>1.52</v>
@@ -19644,10 +19644,10 @@
         <v>18</v>
       </c>
       <c r="H60">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I60">
-        <v>62.16</v>
+        <v>62.58</v>
       </c>
       <c r="J60">
         <v>1.52</v>
@@ -19685,10 +19685,10 @@
         <v>18</v>
       </c>
       <c r="H61">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I61">
-        <v>54.08</v>
+        <v>54.45</v>
       </c>
       <c r="J61">
         <v>1.53</v>
@@ -19761,10 +19761,10 @@
         <v>18</v>
       </c>
       <c r="H63">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I63">
-        <v>68.66</v>
+        <v>69.12</v>
       </c>
       <c r="J63">
         <v>1.53</v>
@@ -19802,10 +19802,10 @@
         <v>18</v>
       </c>
       <c r="H64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I64">
-        <v>61.4</v>
+        <v>61.82</v>
       </c>
       <c r="J64">
         <v>1.52</v>
@@ -19843,10 +19843,10 @@
         <v>18</v>
       </c>
       <c r="H65">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I65">
-        <v>51.79</v>
+        <v>52.13</v>
       </c>
       <c r="J65">
         <v>1.54</v>
@@ -19884,10 +19884,10 @@
         <v>18</v>
       </c>
       <c r="H66">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I66">
-        <v>63.28</v>
+        <v>63.7</v>
       </c>
       <c r="J66">
         <v>1.55</v>
@@ -21055,10 +21055,10 @@
         <v>18</v>
       </c>
       <c r="H95">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I95">
-        <v>68.8</v>
+        <v>69.23</v>
       </c>
       <c r="J95">
         <v>1.62</v>
@@ -22318,10 +22318,10 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I9">
-        <v>58.62</v>
+        <v>59</v>
       </c>
       <c r="J9">
         <v>1.56</v>
@@ -22441,10 +22441,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I12">
-        <v>51.45</v>
+        <v>51.78</v>
       </c>
       <c r="J12">
         <v>1.57</v>
@@ -22902,10 +22902,10 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I7">
-        <v>151.97999999999999</v>
+        <v>153.05000000000001</v>
       </c>
       <c r="J7">
         <v>1.47</v>
@@ -26751,10 +26751,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I16">
-        <v>113.25</v>
+        <v>114.05</v>
       </c>
       <c r="J16">
         <v>1.45</v>
@@ -26792,10 +26792,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I17">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J17">
         <v>1.45</v>
@@ -26833,10 +26833,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I18">
-        <v>58.35</v>
+        <v>58.77</v>
       </c>
       <c r="J18">
         <v>1.45</v>
@@ -26874,10 +26874,10 @@
         <v>18</v>
       </c>
       <c r="H19">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I19">
-        <v>53.08</v>
+        <v>53.45</v>
       </c>
       <c r="J19">
         <v>1.48</v>
@@ -26997,10 +26997,10 @@
         <v>18</v>
       </c>
       <c r="H22">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I22">
-        <v>110.29</v>
+        <v>111.04</v>
       </c>
       <c r="J22">
         <v>1.53</v>
@@ -27038,10 +27038,10 @@
         <v>18</v>
       </c>
       <c r="H23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I23">
-        <v>145.72</v>
+        <v>146.71</v>
       </c>
       <c r="J23">
         <v>1.52</v>
@@ -27079,10 +27079,10 @@
         <v>18</v>
       </c>
       <c r="H24">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I24">
-        <v>86.93</v>
+        <v>87.5</v>
       </c>
       <c r="J24">
         <v>1.55</v>
@@ -27776,10 +27776,10 @@
         <v>18</v>
       </c>
       <c r="H41">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I41">
-        <v>34.49</v>
+        <v>34.71</v>
       </c>
       <c r="J41">
         <v>1.63</v>
@@ -27817,10 +27817,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I42">
-        <v>102.68</v>
+        <v>103.32</v>
       </c>
       <c r="J42">
         <v>1.63</v>
@@ -28872,10 +28872,10 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I7">
-        <v>71.510000000000005</v>
+        <v>72.010000000000005</v>
       </c>
       <c r="J7">
         <v>1.48</v>
@@ -29549,10 +29549,10 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I9">
-        <v>52.61</v>
+        <v>52.99</v>
       </c>
       <c r="J9">
         <v>1.46</v>
@@ -29625,10 +29625,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I11">
-        <v>59.12</v>
+        <v>59.53</v>
       </c>
       <c r="J11">
         <v>1.49</v>
@@ -29806,10 +29806,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I16">
-        <v>58.54</v>
+        <v>58.92</v>
       </c>
       <c r="J16">
         <v>1.6</v>
@@ -30318,6 +30318,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:M111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -32023,10 +32026,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I42">
-        <v>245.35</v>
+        <v>247.1</v>
       </c>
       <c r="J42">
         <v>1.49</v>
@@ -32105,10 +32108,10 @@
         <v>18</v>
       </c>
       <c r="H44">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I44">
-        <v>78.27</v>
+        <v>78.83</v>
       </c>
       <c r="J44">
         <v>1.45</v>
@@ -32187,10 +32190,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I46">
-        <v>66.739999999999995</v>
+        <v>67.209999999999994</v>
       </c>
       <c r="J46">
         <v>1.49</v>
@@ -32228,10 +32231,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I47">
-        <v>339.38</v>
+        <v>341.77</v>
       </c>
       <c r="J47">
         <v>1.49</v>
@@ -32269,10 +32272,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I48">
-        <v>320.02</v>
+        <v>322.27999999999997</v>
       </c>
       <c r="J48">
         <v>1.49</v>
@@ -32761,10 +32764,10 @@
         <v>18</v>
       </c>
       <c r="H60">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I60">
-        <v>458.85</v>
+        <v>461.95</v>
       </c>
       <c r="J60">
         <v>1.54</v>
@@ -32843,10 +32846,10 @@
         <v>18</v>
       </c>
       <c r="H62">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I62">
-        <v>321.16000000000003</v>
+        <v>323.33</v>
       </c>
       <c r="J62">
         <v>1.54</v>
@@ -32884,10 +32887,10 @@
         <v>18</v>
       </c>
       <c r="H63">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I63">
-        <v>338.3</v>
+        <v>340.59</v>
       </c>
       <c r="J63">
         <v>1.53</v>
@@ -32925,10 +32928,10 @@
         <v>18</v>
       </c>
       <c r="H64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I64">
-        <v>82.24</v>
+        <v>82.8</v>
       </c>
       <c r="J64">
         <v>1.53</v>
@@ -32966,10 +32969,10 @@
         <v>18</v>
       </c>
       <c r="H65">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I65">
-        <v>68.42</v>
+        <v>68.89</v>
       </c>
       <c r="J65">
         <v>1.51</v>
@@ -33007,10 +33010,10 @@
         <v>18</v>
       </c>
       <c r="H66">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I66">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J66">
         <v>1.56</v>
@@ -33335,10 +33338,10 @@
         <v>18</v>
       </c>
       <c r="H74">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I74">
-        <v>101.64</v>
+        <v>102.3</v>
       </c>
       <c r="J74">
         <v>1.59</v>
@@ -33376,10 +33379,10 @@
         <v>18</v>
       </c>
       <c r="H75">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I75">
-        <v>237.66</v>
+        <v>239.2</v>
       </c>
       <c r="J75">
         <v>1.58</v>
@@ -34442,10 +34445,10 @@
         <v>18</v>
       </c>
       <c r="H101">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I101">
-        <v>283.07</v>
+        <v>284.83999999999997</v>
       </c>
       <c r="J101">
         <v>1.63</v>
@@ -34483,10 +34486,10 @@
         <v>18</v>
       </c>
       <c r="H102">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I102">
-        <v>295.87</v>
+        <v>297.72000000000003</v>
       </c>
       <c r="J102">
         <v>1.63</v>
@@ -34524,10 +34527,10 @@
         <v>18</v>
       </c>
       <c r="H103">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I103">
-        <v>355.2</v>
+        <v>357.42</v>
       </c>
       <c r="J103">
         <v>1.63</v>
@@ -35160,10 +35163,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I8">
-        <v>72.69</v>
+        <v>73.2</v>
       </c>
       <c r="J8">
         <v>1.47</v>
@@ -35201,10 +35204,10 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I9">
-        <v>84.96</v>
+        <v>85.56</v>
       </c>
       <c r="J9">
         <v>1.49</v>
@@ -35242,10 +35245,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I10">
-        <v>84.64</v>
+        <v>85.21</v>
       </c>
       <c r="J10">
         <v>1.53</v>
@@ -37183,10 +37186,10 @@
         <v>18</v>
       </c>
       <c r="H37">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I37">
-        <v>57.24</v>
+        <v>57.65</v>
       </c>
       <c r="J37">
         <v>1.47</v>
@@ -37224,10 +37227,10 @@
         <v>18</v>
       </c>
       <c r="H38">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I38">
-        <v>61.71</v>
+        <v>62.15</v>
       </c>
       <c r="J38">
         <v>1.47</v>
@@ -37265,10 +37268,10 @@
         <v>18</v>
       </c>
       <c r="H39">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I39">
-        <v>73.02</v>
+        <v>73.540000000000006</v>
       </c>
       <c r="J39">
         <v>1.47</v>
@@ -37306,10 +37309,10 @@
         <v>18</v>
       </c>
       <c r="H40">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I40">
-        <v>93.37</v>
+        <v>94.03</v>
       </c>
       <c r="J40">
         <v>1.47</v>
@@ -37382,10 +37385,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I42">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="J42">
         <v>1.48</v>
@@ -37423,10 +37426,10 @@
         <v>18</v>
       </c>
       <c r="H43">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I43">
-        <v>99.02</v>
+        <v>99.71</v>
       </c>
       <c r="J43">
         <v>1.48</v>
@@ -37464,10 +37467,10 @@
         <v>18</v>
       </c>
       <c r="H44">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I44">
-        <v>70.8</v>
+        <v>71.3</v>
       </c>
       <c r="J44">
         <v>1.49</v>
@@ -37505,10 +37508,10 @@
         <v>18</v>
       </c>
       <c r="H45">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I45">
-        <v>95.1</v>
+        <v>95.77</v>
       </c>
       <c r="J45">
         <v>1.46</v>
@@ -37546,10 +37549,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I46">
-        <v>97.19</v>
+        <v>97.88</v>
       </c>
       <c r="J46">
         <v>1.48</v>
@@ -37587,10 +37590,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I47">
-        <v>87.04</v>
+        <v>87.66</v>
       </c>
       <c r="J47">
         <v>1.47</v>
@@ -37628,10 +37631,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I48">
-        <v>25.46</v>
+        <v>25.64</v>
       </c>
       <c r="J48">
         <v>1.47</v>
@@ -37669,10 +37672,10 @@
         <v>18</v>
       </c>
       <c r="H49">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I49">
-        <v>84.84</v>
+        <v>85.44</v>
       </c>
       <c r="J49">
         <v>1.47</v>
@@ -38026,10 +38029,10 @@
         <v>18</v>
       </c>
       <c r="H58">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I58">
-        <v>96.7</v>
+        <v>97.35</v>
       </c>
       <c r="J58">
         <v>1.54</v>
@@ -38067,10 +38070,10 @@
         <v>18</v>
       </c>
       <c r="H59">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I59">
-        <v>99.68</v>
+        <v>100.36</v>
       </c>
       <c r="J59">
         <v>1.53</v>
@@ -38108,10 +38111,10 @@
         <v>18</v>
       </c>
       <c r="H60">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I60">
-        <v>107.21</v>
+        <v>107.94</v>
       </c>
       <c r="J60">
         <v>1.56</v>
@@ -38149,10 +38152,10 @@
         <v>18</v>
       </c>
       <c r="H61">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I61">
-        <v>78.52</v>
+        <v>79.040000000000006</v>
       </c>
       <c r="J61">
         <v>1.56</v>
@@ -38190,10 +38193,10 @@
         <v>18</v>
       </c>
       <c r="H62">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I62">
-        <v>91.55</v>
+        <v>92.15</v>
       </c>
       <c r="J62">
         <v>1.56</v>
@@ -38231,10 +38234,10 @@
         <v>18</v>
       </c>
       <c r="H63">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I63">
-        <v>106.63</v>
+        <v>107.34</v>
       </c>
       <c r="J63">
         <v>1.55</v>
@@ -39168,10 +39171,10 @@
         <v>18</v>
       </c>
       <c r="H86">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I86">
-        <v>96.38</v>
+        <v>96.98</v>
       </c>
       <c r="J86">
         <v>1.63</v>
@@ -39209,10 +39212,10 @@
         <v>18</v>
       </c>
       <c r="H87">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I87">
-        <v>83.86</v>
+        <v>84.38</v>
       </c>
       <c r="J87">
         <v>1.63</v>
@@ -39250,10 +39253,10 @@
         <v>18</v>
       </c>
       <c r="H88">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I88">
-        <v>126.12</v>
+        <v>126.9</v>
       </c>
       <c r="J88">
         <v>1.63</v>
@@ -40197,10 +40200,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I8">
-        <v>37.19</v>
+        <v>37.43</v>
       </c>
       <c r="J8">
         <v>1.59</v>
@@ -42128,10 +42131,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I42">
-        <v>88.33</v>
+        <v>88.96</v>
       </c>
       <c r="J42">
         <v>1.47</v>
@@ -42169,10 +42172,10 @@
         <v>18</v>
       </c>
       <c r="H43">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I43">
-        <v>65.69</v>
+        <v>66.150000000000006</v>
       </c>
       <c r="J43">
         <v>1.47</v>
@@ -42210,10 +42213,10 @@
         <v>18</v>
       </c>
       <c r="H44">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I44">
-        <v>45.39</v>
+        <v>45.72</v>
       </c>
       <c r="J44">
         <v>1.47</v>
@@ -42251,10 +42254,10 @@
         <v>18</v>
       </c>
       <c r="H45">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I45">
-        <v>83.93</v>
+        <v>84.53</v>
       </c>
       <c r="J45">
         <v>1.46</v>
@@ -42292,10 +42295,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I46">
-        <v>55.69</v>
+        <v>56.09</v>
       </c>
       <c r="J46">
         <v>1.49</v>
@@ -42333,10 +42336,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I47">
-        <v>63.28</v>
+        <v>63.73</v>
       </c>
       <c r="J47">
         <v>1.47</v>
@@ -42374,10 +42377,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I48">
-        <v>82.07</v>
+        <v>82.65</v>
       </c>
       <c r="J48">
         <v>1.48</v>
@@ -42415,10 +42418,10 @@
         <v>18</v>
       </c>
       <c r="H49">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I49">
-        <v>47.18</v>
+        <v>47.52</v>
       </c>
       <c r="J49">
         <v>1.49</v>
@@ -42456,10 +42459,10 @@
         <v>18</v>
       </c>
       <c r="H50">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I50">
-        <v>74.13</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="J50">
         <v>1.49</v>
@@ -42497,10 +42500,10 @@
         <v>18</v>
       </c>
       <c r="H51">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I51">
-        <v>125.47</v>
+        <v>126.36</v>
       </c>
       <c r="J51">
         <v>1.49</v>
@@ -42538,10 +42541,10 @@
         <v>18</v>
       </c>
       <c r="H52">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I52">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="J52">
         <v>1.49</v>
@@ -43071,10 +43074,10 @@
         <v>18</v>
       </c>
       <c r="H65">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I65">
-        <v>99.22</v>
+        <v>99.89</v>
       </c>
       <c r="J65">
         <v>1.54</v>
@@ -43112,10 +43115,10 @@
         <v>18</v>
       </c>
       <c r="H66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I66">
-        <v>51.71</v>
+        <v>52.04</v>
       </c>
       <c r="J66">
         <v>1.8</v>
@@ -43153,10 +43156,10 @@
         <v>18</v>
       </c>
       <c r="H67">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I67">
-        <v>45.87</v>
+        <v>46.17</v>
       </c>
       <c r="J67">
         <v>1.56</v>
@@ -43235,10 +43238,10 @@
         <v>18</v>
       </c>
       <c r="H69">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I69">
-        <v>84.32</v>
+        <v>84.88</v>
       </c>
       <c r="J69">
         <v>1.56</v>
@@ -43276,10 +43279,10 @@
         <v>18</v>
       </c>
       <c r="H70">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I70">
-        <v>80.89</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="J70">
         <v>1.54</v>
@@ -43358,10 +43361,10 @@
         <v>18</v>
       </c>
       <c r="H72">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I72">
-        <v>147.69999999999999</v>
+        <v>148.68</v>
       </c>
       <c r="J72">
         <v>1.53</v>
@@ -43434,10 +43437,10 @@
         <v>18</v>
       </c>
       <c r="H74">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I74">
-        <v>47.11</v>
+        <v>47.42</v>
       </c>
       <c r="J74">
         <v>1.56</v>
@@ -43475,10 +43478,10 @@
         <v>18</v>
       </c>
       <c r="H75">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I75">
-        <v>51.69</v>
+        <v>52.03</v>
       </c>
       <c r="J75">
         <v>1.56</v>
@@ -43762,10 +43765,10 @@
         <v>18</v>
       </c>
       <c r="H82">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I82">
-        <v>131.69</v>
+        <v>132.49</v>
       </c>
       <c r="J82">
         <v>1.86</v>
@@ -43803,10 +43806,10 @@
         <v>18</v>
       </c>
       <c r="H83">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I83">
-        <v>131.69</v>
+        <v>132.49</v>
       </c>
       <c r="J83">
         <v>1.86</v>
@@ -43844,10 +43847,10 @@
         <v>18</v>
       </c>
       <c r="H84">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I84">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="J84">
         <v>1.86</v>
@@ -43885,10 +43888,10 @@
         <v>18</v>
       </c>
       <c r="H85">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I85">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="J85">
         <v>1.86</v>
@@ -44254,10 +44257,10 @@
         <v>18</v>
       </c>
       <c r="H94">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I94">
-        <v>73.39</v>
+        <v>73.83</v>
       </c>
       <c r="J94">
         <v>1.86</v>
@@ -44295,10 +44298,10 @@
         <v>18</v>
       </c>
       <c r="H95">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I95">
-        <v>73.39</v>
+        <v>73.83</v>
       </c>
       <c r="J95">
         <v>1.86</v>
@@ -44945,10 +44948,10 @@
         <v>18</v>
       </c>
       <c r="H111">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I111">
-        <v>59.99</v>
+        <v>60.36</v>
       </c>
       <c r="J111">
         <v>1.63</v>
@@ -45597,13 +45600,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -46223,10 +46219,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I10">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="J10">
         <v>1.49</v>
@@ -46264,10 +46260,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I11">
-        <v>1260</v>
+        <v>1269</v>
       </c>
       <c r="J11">
         <v>1.47</v>
@@ -46305,10 +46301,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I12">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="J12">
         <v>1.49</v>
@@ -46346,10 +46342,10 @@
         <v>18</v>
       </c>
       <c r="H13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I13">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="J13">
         <v>1.49</v>
@@ -46387,10 +46383,10 @@
         <v>18</v>
       </c>
       <c r="H14">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I14">
-        <v>63.83</v>
+        <v>64.28</v>
       </c>
       <c r="J14">
         <v>1.49</v>
@@ -49560,10 +49556,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I8">
-        <v>19.649999999999999</v>
+        <v>19.77</v>
       </c>
       <c r="J8">
         <v>1.63</v>
@@ -50249,10 +50245,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I17">
-        <v>74.34</v>
+        <v>74.88</v>
       </c>
       <c r="J17">
         <v>1.45</v>
@@ -50290,10 +50286,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I18">
-        <v>29.67</v>
+        <v>29.88</v>
       </c>
       <c r="J18">
         <v>1.47</v>
@@ -50331,10 +50327,10 @@
         <v>18</v>
       </c>
       <c r="H19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I19">
-        <v>79.84</v>
+        <v>80.41</v>
       </c>
       <c r="J19">
         <v>1.44</v>
@@ -50372,10 +50368,10 @@
         <v>18</v>
       </c>
       <c r="H20">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I20">
-        <v>59.11</v>
+        <v>59.53</v>
       </c>
       <c r="J20">
         <v>1.48</v>
@@ -50413,10 +50409,10 @@
         <v>18</v>
       </c>
       <c r="H21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I21">
-        <v>90.39</v>
+        <v>91.02</v>
       </c>
       <c r="J21">
         <v>1.47</v>
@@ -50571,10 +50567,10 @@
         <v>18</v>
       </c>
       <c r="H25">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I25">
-        <v>22.51</v>
+        <v>22.66</v>
       </c>
       <c r="J25">
         <v>1.53</v>
@@ -50612,10 +50608,10 @@
         <v>18</v>
       </c>
       <c r="H26">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I26">
-        <v>84.52</v>
+        <v>85.1</v>
       </c>
       <c r="J26">
         <v>1.53</v>
@@ -50653,10 +50649,10 @@
         <v>18</v>
       </c>
       <c r="H27">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I27">
-        <v>47.1</v>
+        <v>47.41</v>
       </c>
       <c r="J27">
         <v>1.52</v>
@@ -50694,10 +50690,10 @@
         <v>18</v>
       </c>
       <c r="H28">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I28">
-        <v>114.76</v>
+        <v>115.52</v>
       </c>
       <c r="J28">
         <v>1.56</v>
@@ -50735,10 +50731,10 @@
         <v>18</v>
       </c>
       <c r="H29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I29">
-        <v>123.54</v>
+        <v>124.36</v>
       </c>
       <c r="J29">
         <v>1.53</v>
@@ -50776,10 +50772,10 @@
         <v>18</v>
       </c>
       <c r="H30">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I30">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="J30">
         <v>1.56</v>
@@ -51947,10 +51943,10 @@
         <v>18</v>
       </c>
       <c r="H59">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I59">
-        <v>26.06</v>
+        <v>26.22</v>
       </c>
       <c r="J59">
         <v>1.63</v>
